--- a/4 четверть_27_Javascript_Infisical.xlsx
+++ b/4 четверть_27_Javascript_Infisical.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\AlexServHW\Desktop\GB_Developer_Workbook\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7E9B98F-AF43-4255-AD34-EB00C7ED5898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E70B34D9-2F7E-493F-B7B1-3D9F25D18F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2304" yWindow="1248" windowWidth="23016" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="24" yWindow="1152" windowWidth="23016" windowHeight="11136" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Название 1-3" sheetId="12" r:id="rId1"/>
@@ -65,10 +65,6 @@
     <t>Один раз</t>
   </si>
   <si>
-    <t>cd /path/to/project
-infisical init</t>
-  </si>
-  <si>
     <t>The infisical init command creates a .infisical.json file, containing local project settings, at the location where the command is executed.</t>
   </si>
   <si>
@@ -347,12 +343,30 @@
   <si>
     <t>Инициализация в проекте</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">cd /path/to/project
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="204"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>infisical init</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -444,6 +458,15 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF7030A0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="204"/>
@@ -494,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -537,6 +560,9 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -962,41 +988,41 @@
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A9" s="14" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1"/>
     </row>
     <row r="10" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C11" s="9" t="s">
         <v>15</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A12" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A13" s="9" t="s">
+      <c r="A13" s="16" t="s">
         <v>7</v>
       </c>
       <c r="B13" s="2" t="s">
@@ -1008,44 +1034,44 @@
     </row>
     <row r="14" spans="1:21" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" s="15" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="100.8" x14ac:dyDescent="0.3">
       <c r="C15" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="144" x14ac:dyDescent="0.3">
       <c r="B17" s="9" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="57.6" x14ac:dyDescent="0.3">
       <c r="B19" s="13" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
